--- a/docs/todo/kakao-account-recovery-todo.xlsx
+++ b/docs/todo/kakao-account-recovery-todo.xlsx
@@ -47,7 +47,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -70,18 +70,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00EEEEEE"/>
         <bgColor rgb="00EEEEEE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
-        <bgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -111,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -130,12 +118,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -503,15 +485,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -536,295 +517,49 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>구분</t>
+          <t>이슈</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>작업 내용</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>우선순위</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>우선순위</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
           <t>상태</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="110" customHeight="1">
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>백엔드</t>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>카카오 계정 복구 기능</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>가입 실패(사업자번호 중복) 시 복구 요청 플래그 반환</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>signupForOauth에서 bizRegNo 중복 예외 발생 시, 프론트가 '복구 요청' 버튼을 띄울 수 있도록 응답 코드/메시지 구분</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
+          <t>1) 사업자번호 중복으로 카카오 재가입 실패 시, 에러로 끝내지 않고 '계정 복구 요청'을 남길 수 있게 처리
+2) 복구 요청 정보(새 카카오 계정 식별값 + 사업자등록번호)를 임시 저장
+3) 슈퍼관리자가 복구 요청 목록을 조회하고, 사업자 정보(대표자명/연락처 등) 대조 후 승인
+4) 승인 시 기존 계정의 카카오 연동 정보를 새 카카오 계정으로 교체
+5) 정상 흐름 및 악용 방지(본인확인 없는 임의 요청 차단) 테스트</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>미착수</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>백엔드</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>복구 요청 저장소 추가</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>OauthPendingSignupStore와 유사하게 (signupToken/새 providerUserId, bizRegNo, 요청일시) 임시 저장 - 신규 컴포넌트 또는 테이블</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>미착수</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>백엔드</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>복구 요청 API 추가</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>POST /api/biz/signup/kakao/recover - signupToken + bizRegNo를 받아 복구 요청 생성, 인증 제외 경로 등록</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>미착수</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>백엔드</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>슈퍼관리자 복구 요청 승인 API</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>요청 승인 시 tb_admin_oauth의 기존 provider_user_id row를 새 값으로 교체(재연결)</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>미착수</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>프론트</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>가입 화면에 '계정 복구 요청' 버튼 추가</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>사업자번호 중복 에러 시 기존 에러 문구 대신 복구 요청 버튼 노출 (AdminKakaoCallback.jsx)</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>미착수</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>프론트</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>슈퍼관리자 - 복구 요청 목록/승인 화면</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>대기중인 복구 요청 목록 조회, 사업자 정보 대조 후 승인/거절 처리 UI</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>미착수</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>정책</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>본인확인 방법 정의</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>승인 전 대표자명/연락처 등 어떤 정보로 신원을 대조할지 기준 확정 필요</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>미착수</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>테스트</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>정상 흐름 검증</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>새 카카오 계정으로 로그인 시도 -&gt; 복구 요청 -&gt; 승인 -&gt; 새 계정으로 정상 로그인되는지 확인</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>낮음</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>미착수</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>테스트</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>악용 방지 검증</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>타인이 임의로 타 사업자번호에 대해 복구 요청을 남발하지 못하도록 제한/알림 확인</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>낮음</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>미착수</t>
         </is>
@@ -832,8 +567,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
